--- a/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T14:37:21+00:00</t>
+    <t>2025-01-06T16:21:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:21:28+00:00</t>
+    <t>2025-01-07T10:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T10:53:29+00:00</t>
+    <t>2025-01-07T12:05:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T12:05:20+00:00</t>
+    <t>2025-01-10T09:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Property</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-10T09:39:42+00:00</t>
+    <t>2025-01-20T10:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,7 +316,9 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">

--- a/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-X10-AgregatCategorieEtablissement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T10:44:30+00:00</t>
+    <t>2025-01-31T15:38:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
